--- a/Книга1.xlsx
+++ b/Книга1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vasya\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vasya\Documents\колледж\Диплом\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D562D8E-15DA-4735-B7E1-1FA9AC75AB20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A0773D6-BB2A-438C-87FA-B3398E2529DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11385" xr2:uid="{2E93A248-6FA2-4A11-8E82-5754573AC094}"/>
+    <workbookView xWindow="5520" yWindow="3000" windowWidth="13710" windowHeight="6540" xr2:uid="{2E93A248-6FA2-4A11-8E82-5754573AC094}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="40">
   <si>
     <t>Фамилия</t>
   </si>
@@ -54,27 +54,9 @@
     <t>Школа</t>
   </si>
   <si>
-    <t>Иванов</t>
-  </si>
-  <si>
-    <t>Иван</t>
-  </si>
-  <si>
-    <t>Иванович</t>
-  </si>
-  <si>
     <t>МБОУ СОШ №55</t>
   </si>
   <si>
-    <t>Петрова</t>
-  </si>
-  <si>
-    <t>Анна</t>
-  </si>
-  <si>
-    <t>Сергеевна</t>
-  </si>
-  <si>
     <t>Мбоу Сош 55</t>
   </si>
   <si>
@@ -157,6 +139,24 @@
   </si>
   <si>
     <t>Андрей</t>
+  </si>
+  <si>
+    <t>Прохожев</t>
+  </si>
+  <si>
+    <t>Василий</t>
+  </si>
+  <si>
+    <t>Алексеевич</t>
+  </si>
+  <si>
+    <t>Петров</t>
+  </si>
+  <si>
+    <t>Сергеевич</t>
+  </si>
+  <si>
+    <t>3.0</t>
   </si>
 </sst>
 </file>
@@ -188,12 +188,27 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -202,9 +217,9 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="12" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="12" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -534,171 +549,173 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H1" t="s">
-        <v>24</v>
-      </c>
-      <c r="I1" t="s">
-        <v>25</v>
+      <c r="H1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2" s="2">
+        <v>38993</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="1">
-        <v>38487</v>
-      </c>
-      <c r="E2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" t="s">
-        <v>28</v>
-      </c>
-      <c r="I2" s="2">
-        <v>46146</v>
+      <c r="H2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="1">
+      <c r="A3" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" s="2">
         <v>38796</v>
       </c>
-      <c r="E3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I3" s="2">
-        <v>46057</v>
+      <c r="E3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="A4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="2">
+        <v>38666</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>39</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="1">
-        <v>38666</v>
-      </c>
-      <c r="E4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F4" t="s">
-        <v>32</v>
-      </c>
-      <c r="G4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" t="s">
-        <v>33</v>
-      </c>
-      <c r="I4" s="2">
-        <v>46237</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="1">
+      <c r="A5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="2">
         <v>38899</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F5" t="s">
-        <v>34</v>
-      </c>
-      <c r="G5" t="s">
-        <v>18</v>
-      </c>
-      <c r="H5" t="s">
-        <v>35</v>
-      </c>
       <c r="I5" s="3" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="1"/>
+      <c r="D6" s="2">
+        <v>38607</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="1">
-        <v>38607</v>
-      </c>
-      <c r="E6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G6" t="s">
-        <v>21</v>
-      </c>
-      <c r="H6" t="s">
-        <v>37</v>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
